--- a/utils/monday_sprint_sprint_2024-41.xlsx
+++ b/utils/monday_sprint_sprint_2024-41.xlsx
@@ -162,7 +162,7 @@
     <t>25/04/2023</t>
   </si>
   <si>
-    <t>23/02/2026</t>
+    <t>18/02/2026</t>
   </si>
   <si>
     <t>Abril</t>
@@ -2903,7 +2903,7 @@
         <v>37</v>
       </c>
       <c r="Q11">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="4:17" x14ac:dyDescent="0.25">
@@ -2929,7 +2929,7 @@
         <v>26</v>
       </c>
       <c r="Q12">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="7:17" x14ac:dyDescent="0.25">
@@ -3017,7 +3017,7 @@
         <v>15</v>
       </c>
       <c r="F21" s="2">
-        <v>1020</v>
+        <v>1015</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>45</v>
@@ -3031,7 +3031,7 @@
         <v>15</v>
       </c>
       <c r="F22" s="2">
-        <v>920</v>
+        <v>923</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>18</v>

--- a/utils/monday_sprint_sprint_2024-41.xlsx
+++ b/utils/monday_sprint_sprint_2024-41.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="697" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="696" uniqueCount="166">
   <si>
     <t>Ticket</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Equipe TI</t>
   </si>
   <si>
-    <t>Entrada Sprint</t>
+    <t>Abertura</t>
   </si>
   <si>
     <t>Encerramento</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>SLA (15 dias)</t>
+    <t>Dentro da SLA</t>
   </si>
   <si>
     <t>Semana</t>
@@ -90,7 +90,7 @@
     <t>08/07/2024</t>
   </si>
   <si>
-    <t>N/A</t>
+    <t>01/08/2024</t>
   </si>
   <si>
     <t>Implantação</t>
@@ -105,7 +105,7 @@
     <t>Julho</t>
   </si>
   <si>
-    <t>25131</t>
+    <t>7122867829</t>
   </si>
   <si>
     <t>Setor não informado</t>
@@ -129,13 +129,16 @@
     <t>30/07/2024</t>
   </si>
   <si>
+    <t>04/08/2024</t>
+  </si>
+  <si>
     <t>Feito</t>
   </si>
   <si>
     <t>Semana 5</t>
   </si>
   <si>
-    <t>27114</t>
+    <t>7078352398</t>
   </si>
   <si>
     <t>Criar campo permite Alterar Avaliação Checklist</t>
@@ -144,10 +147,13 @@
     <t>23/07/2024</t>
   </si>
   <si>
+    <t>28/07/2024</t>
+  </si>
+  <si>
     <t>Semana 4</t>
   </si>
   <si>
-    <t>26571</t>
+    <t>6883850772</t>
   </si>
   <si>
     <t>Retirar peças do deposito para versão Web - Tabelas e Procedimentos</t>
@@ -162,13 +168,16 @@
     <t>Junho</t>
   </si>
   <si>
-    <t>26512</t>
+    <t>6883950820</t>
   </si>
   <si>
     <t>ERP X Alea</t>
   </si>
   <si>
-    <t>26510</t>
+    <t>31/07/2024</t>
+  </si>
+  <si>
+    <t>6900454835</t>
   </si>
   <si>
     <t>Relatório Promissórias - PROEX</t>
@@ -177,19 +186,25 @@
     <t>25/06/2024</t>
   </si>
   <si>
+    <t>6883975426</t>
+  </si>
+  <si>
     <t>PROJETO SISTEMA PROEX</t>
   </si>
   <si>
+    <t>6900457023</t>
+  </si>
+  <si>
     <t>Relatório Borderô de exportação - PROEX</t>
   </si>
   <si>
-    <t>19909</t>
+    <t>6980010750</t>
   </si>
   <si>
     <t>Registro de Pintura</t>
   </si>
   <si>
-    <t>26637</t>
+    <t>6989511588</t>
   </si>
   <si>
     <t>Iniciar uma parada sem necessitar estar apontado em alguma sequencia (exemplo, operador inicia o turno preenchendo a MPO); Usar a AA001</t>
@@ -198,22 +213,22 @@
     <t>09/07/2024</t>
   </si>
   <si>
-    <t>24746</t>
+    <t>22/07/2024</t>
+  </si>
+  <si>
+    <t>7069493408</t>
   </si>
   <si>
     <t>Abrir possibilidade de dada de parcelamentos adantamentos (100)</t>
   </si>
   <si>
-    <t>22/07/2024</t>
-  </si>
-  <si>
-    <t>26937</t>
+    <t>7069465160</t>
   </si>
   <si>
     <t>Importação Planilha do Ronda</t>
   </si>
   <si>
-    <t>25360</t>
+    <t>6350648403</t>
   </si>
   <si>
     <t>Gestão à vista rebarbação VI - Motivo tempo excedido</t>
@@ -225,7 +240,7 @@
     <t>Março</t>
   </si>
   <si>
-    <t>26829</t>
+    <t>7113182305</t>
   </si>
   <si>
     <t>Segregação custeiro - Fundição - 5.1.2.01.106-Eletrodos de grafite</t>
@@ -234,31 +249,49 @@
     <t>29/07/2024</t>
   </si>
   <si>
+    <t>7113186434</t>
+  </si>
+  <si>
     <t>Segregação custeiro - Fundição - 5.1.2.01.108-Tintas refratárias</t>
   </si>
   <si>
+    <t>7136126771</t>
+  </si>
+  <si>
     <t>Segregação custeio - Fundição - 5.1.2.01.196 - MATERIAIS AUXILIARES (Tipo MAT.AUX.)</t>
   </si>
   <si>
-    <t>31/07/2024</t>
+    <t>7069513380</t>
   </si>
   <si>
     <t>No report do CPC colocar quadro com eventos de pagamentos</t>
   </si>
   <si>
+    <t>7069506122</t>
+  </si>
+  <si>
     <t>Informar data ao inves n° de dias tea eventos</t>
   </si>
   <si>
+    <t>7122857464</t>
+  </si>
+  <si>
     <t>Criar tabela ponte com as informações para montagem do MRP e depois usar na migração dos dados para o Nimbi pela API que será fornecida pela Silvia.</t>
   </si>
   <si>
+    <t>7113170454</t>
+  </si>
+  <si>
     <t>Segregação custeiro - Fundição - 5.1.2.01.112-Massas refratárias / 5.1.2.01.114-Refratários básicos</t>
   </si>
   <si>
+    <t>7113168058</t>
+  </si>
+  <si>
     <t>Segregação custeiro - Fundição - 5.1.2.03.502-Energia elétrica</t>
   </si>
   <si>
-    <t>26487</t>
+    <t>7068744507</t>
   </si>
   <si>
     <t>Correção</t>
@@ -267,7 +300,7 @@
     <t>Falha em campo de observações do AP-119</t>
   </si>
   <si>
-    <t>26949</t>
+    <t>7060780697</t>
   </si>
   <si>
     <t>Tempos de Máquina no Planilha MPS</t>
@@ -276,103 +309,106 @@
     <t>19/07/2024</t>
   </si>
   <si>
-    <t>26980</t>
+    <t>7060519900</t>
   </si>
   <si>
     <t>REVISÃO DO FLUXO 105</t>
   </si>
   <si>
-    <t>27017</t>
+    <t>7060491214</t>
   </si>
   <si>
     <t>AUMENTO DE CARACTERES - DESMOLDAGEM</t>
   </si>
   <si>
-    <t>26930</t>
+    <t>7060949969</t>
   </si>
   <si>
     <t>Ajuste de Segmentação de CFOP</t>
   </si>
   <si>
-    <t>26939</t>
+    <t>7060914517</t>
   </si>
   <si>
     <t>Apontamento Ajustagem IIII</t>
   </si>
   <si>
-    <t>26943</t>
+    <t>7060793142</t>
   </si>
   <si>
     <t>Melhoria de sistema - Registro de inspeção Bruto/Rough</t>
   </si>
   <si>
-    <t>26913</t>
+    <t>7060985787</t>
   </si>
   <si>
     <t>Apontamento Ajustagem / Pintura</t>
   </si>
   <si>
-    <t>26908</t>
+    <t>7060999403</t>
   </si>
   <si>
     <t>Erros preenchimento planilhão</t>
   </si>
   <si>
-    <t>26910</t>
+    <t>7060993996</t>
   </si>
   <si>
     <t>Melhoria Sistema Embalagens</t>
   </si>
   <si>
-    <t>26925</t>
+    <t>7060966147</t>
   </si>
   <si>
     <t>Altona || Sistema ERP || Checagem de OSI</t>
   </si>
   <si>
-    <t>26920</t>
+    <t>7060976022</t>
   </si>
   <si>
     <t>Conclusão usinagem no planilhão MPS</t>
   </si>
   <si>
-    <t>27050</t>
+    <t>7060382882</t>
   </si>
   <si>
     <t>Melhorias sistema de Embalagens II</t>
   </si>
   <si>
-    <t>27065</t>
+    <t>7060319964</t>
   </si>
   <si>
     <t>Apontamento Ajustagem III</t>
   </si>
   <si>
-    <t>26898</t>
+    <t>7061015617</t>
   </si>
   <si>
     <t>Agrupamento de lotes no Planilha MPS</t>
   </si>
   <si>
-    <t>27057</t>
+    <t>7060372969</t>
   </si>
   <si>
     <t>MELHORIAS APONTAMENTO ELETRÔNICO</t>
   </si>
   <si>
-    <t>27048</t>
+    <t>03/08/2024</t>
+  </si>
+  <si>
+    <t>7060395931</t>
   </si>
   <si>
     <t>Melhoria sistema de modelo</t>
   </si>
   <si>
-    <t>26881</t>
+    <t>7061046440</t>
   </si>
   <si>
     <t>Trava na Movimentação dos setroes 502/522/504</t>
   </si>
   <si>
-    <t>26721</t>
+    <t>7068687802</t>
   </si>
   <si>
     <t>Controle na geração de Sequencias</t>
@@ -387,7 +423,7 @@
     <t>Período</t>
   </si>
   <si>
-    <t>SPRINT 2024-41</t>
+    <t>Mar/2024</t>
   </si>
   <si>
     <t>Base</t>
@@ -439,6 +475,9 @@
   </si>
   <si>
     <t>Sim</t>
+  </si>
+  <si>
+    <t>Semana 1</t>
   </si>
   <si>
     <t>A fazer</t>
@@ -1032,16 +1071,16 @@
         <v>37</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M3" s="2" t="s">
         <v>27</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O3" s="2" t="s">
         <v>29</v>
@@ -1049,7 +1088,7 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>31</v>
@@ -1061,10 +1100,10 @@
         <v>33</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>21</v>
@@ -1076,19 +1115,19 @@
         <v>36</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M4" s="2" t="s">
         <v>27</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="O4" s="2" t="s">
         <v>29</v>
@@ -1096,7 +1135,7 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>31</v>
@@ -1108,10 +1147,10 @@
         <v>33</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>21</v>
@@ -1123,27 +1162,27 @@
         <v>36</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>25</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M5" s="2" t="s">
         <v>27</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>31</v>
@@ -1155,42 +1194,42 @@
         <v>33</v>
       </c>
       <c r="E6" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N6" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="O6" s="2" t="s">
         <v>50</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="N6" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="O6" s="2" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>31</v>
@@ -1202,10 +1241,10 @@
         <v>33</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>21</v>
@@ -1217,27 +1256,27 @@
         <v>36</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M7" s="2" t="s">
         <v>27</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>31</v>
@@ -1249,10 +1288,10 @@
         <v>33</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>21</v>
@@ -1264,27 +1303,27 @@
         <v>36</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M8" s="2" t="s">
         <v>27</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>31</v>
@@ -1296,10 +1335,10 @@
         <v>33</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>21</v>
@@ -1311,27 +1350,27 @@
         <v>36</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M9" s="2" t="s">
         <v>27</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>31</v>
@@ -1343,10 +1382,10 @@
         <v>33</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>21</v>
@@ -1361,10 +1400,10 @@
         <v>24</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M10" s="2" t="s">
         <v>27</v>
@@ -1378,7 +1417,7 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>31</v>
@@ -1390,10 +1429,10 @@
         <v>33</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>21</v>
@@ -1405,13 +1444,13 @@
         <v>36</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M11" s="2" t="s">
         <v>27</v>
@@ -1425,7 +1464,7 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>31</v>
@@ -1437,10 +1476,10 @@
         <v>33</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>21</v>
@@ -1452,19 +1491,19 @@
         <v>36</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M12" s="2" t="s">
         <v>27</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="O12" s="2" t="s">
         <v>29</v>
@@ -1472,7 +1511,7 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>31</v>
@@ -1484,10 +1523,10 @@
         <v>33</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>21</v>
@@ -1499,10 +1538,10 @@
         <v>36</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>26</v>
@@ -1511,7 +1550,7 @@
         <v>27</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="O13" s="2" t="s">
         <v>29</v>
@@ -1519,7 +1558,7 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>31</v>
@@ -1531,10 +1570,10 @@
         <v>33</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>21</v>
@@ -1546,27 +1585,27 @@
         <v>36</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M14" s="2" t="s">
         <v>27</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>31</v>
@@ -1578,10 +1617,10 @@
         <v>33</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>21</v>
@@ -1593,19 +1632,19 @@
         <v>36</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M15" s="2" t="s">
         <v>27</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O15" s="2" t="s">
         <v>29</v>
@@ -1613,7 +1652,7 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>31</v>
@@ -1625,10 +1664,10 @@
         <v>33</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>21</v>
@@ -1640,19 +1679,19 @@
         <v>36</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>25</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M16" s="2" t="s">
         <v>27</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O16" s="2" t="s">
         <v>29</v>
@@ -1660,7 +1699,7 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>31</v>
@@ -1672,10 +1711,10 @@
         <v>33</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>21</v>
@@ -1687,19 +1726,19 @@
         <v>36</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>75</v>
+        <v>53</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M17" s="2" t="s">
         <v>27</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O17" s="2" t="s">
         <v>29</v>
@@ -1707,7 +1746,7 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>61</v>
+        <v>82</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>31</v>
@@ -1719,10 +1758,10 @@
         <v>33</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>21</v>
@@ -1734,19 +1773,19 @@
         <v>36</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M18" s="2" t="s">
         <v>27</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="O18" s="2" t="s">
         <v>29</v>
@@ -1754,7 +1793,7 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>61</v>
+        <v>84</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>31</v>
@@ -1766,10 +1805,10 @@
         <v>33</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>21</v>
@@ -1781,19 +1820,19 @@
         <v>36</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M19" s="2" t="s">
         <v>27</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="O19" s="2" t="s">
         <v>29</v>
@@ -1801,7 +1840,7 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>30</v>
+        <v>86</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>31</v>
@@ -1813,10 +1852,10 @@
         <v>33</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>21</v>
@@ -1831,16 +1870,16 @@
         <v>37</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M20" s="2" t="s">
         <v>27</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O20" s="2" t="s">
         <v>29</v>
@@ -1848,7 +1887,7 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>31</v>
@@ -1860,10 +1899,10 @@
         <v>33</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>21</v>
@@ -1875,19 +1914,19 @@
         <v>36</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M21" s="2" t="s">
         <v>27</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O21" s="2" t="s">
         <v>29</v>
@@ -1895,7 +1934,7 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>31</v>
@@ -1907,10 +1946,10 @@
         <v>33</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>21</v>
@@ -1922,19 +1961,19 @@
         <v>36</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="K22" s="2" t="s">
         <v>25</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M22" s="2" t="s">
         <v>27</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O22" s="2" t="s">
         <v>29</v>
@@ -1942,22 +1981,22 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>21</v>
@@ -1969,19 +2008,19 @@
         <v>36</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>25</v>
+        <v>77</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M23" s="2" t="s">
         <v>27</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="O23" s="2" t="s">
         <v>29</v>
@@ -1989,7 +2028,7 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>31</v>
@@ -2001,10 +2040,10 @@
         <v>33</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>21</v>
@@ -2016,19 +2055,19 @@
         <v>36</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M24" s="2" t="s">
         <v>27</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O24" s="2" t="s">
         <v>29</v>
@@ -2036,7 +2075,7 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>31</v>
@@ -2048,10 +2087,10 @@
         <v>33</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>21</v>
@@ -2063,19 +2102,19 @@
         <v>36</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M25" s="2" t="s">
         <v>27</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O25" s="2" t="s">
         <v>29</v>
@@ -2083,7 +2122,7 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>31</v>
@@ -2095,10 +2134,10 @@
         <v>33</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>21</v>
@@ -2110,19 +2149,19 @@
         <v>36</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M26" s="2" t="s">
         <v>27</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O26" s="2" t="s">
         <v>29</v>
@@ -2130,7 +2169,7 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>31</v>
@@ -2142,10 +2181,10 @@
         <v>33</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>21</v>
@@ -2157,19 +2196,19 @@
         <v>36</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>25</v>
+        <v>77</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M27" s="2" t="s">
         <v>27</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O27" s="2" t="s">
         <v>29</v>
@@ -2177,7 +2216,7 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>31</v>
@@ -2189,10 +2228,10 @@
         <v>33</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>21</v>
@@ -2204,19 +2243,19 @@
         <v>36</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M28" s="2" t="s">
         <v>27</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O28" s="2" t="s">
         <v>29</v>
@@ -2224,7 +2263,7 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>31</v>
@@ -2236,10 +2275,10 @@
         <v>33</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>21</v>
@@ -2251,19 +2290,19 @@
         <v>36</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M29" s="2" t="s">
         <v>27</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O29" s="2" t="s">
         <v>29</v>
@@ -2271,7 +2310,7 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>31</v>
@@ -2283,10 +2322,10 @@
         <v>33</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>21</v>
@@ -2298,19 +2337,19 @@
         <v>36</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M30" s="2" t="s">
         <v>27</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O30" s="2" t="s">
         <v>29</v>
@@ -2318,7 +2357,7 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>31</v>
@@ -2330,10 +2369,10 @@
         <v>33</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>21</v>
@@ -2345,19 +2384,19 @@
         <v>36</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M31" s="2" t="s">
         <v>27</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O31" s="2" t="s">
         <v>29</v>
@@ -2365,7 +2404,7 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>31</v>
@@ -2377,10 +2416,10 @@
         <v>33</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>21</v>
@@ -2392,19 +2431,19 @@
         <v>36</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M32" s="2" t="s">
         <v>27</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O32" s="2" t="s">
         <v>29</v>
@@ -2412,7 +2451,7 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>31</v>
@@ -2424,10 +2463,10 @@
         <v>33</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>21</v>
@@ -2439,19 +2478,19 @@
         <v>36</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M33" s="2" t="s">
         <v>27</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O33" s="2" t="s">
         <v>29</v>
@@ -2459,7 +2498,7 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>31</v>
@@ -2471,10 +2510,10 @@
         <v>33</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>21</v>
@@ -2486,19 +2525,19 @@
         <v>36</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M34" s="2" t="s">
         <v>27</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O34" s="2" t="s">
         <v>29</v>
@@ -2506,7 +2545,7 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>31</v>
@@ -2518,10 +2557,10 @@
         <v>33</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>21</v>
@@ -2533,19 +2572,19 @@
         <v>36</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>25</v>
+        <v>77</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M35" s="2" t="s">
         <v>27</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O35" s="2" t="s">
         <v>29</v>
@@ -2553,7 +2592,7 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>31</v>
@@ -2565,10 +2604,10 @@
         <v>33</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>21</v>
@@ -2580,19 +2619,19 @@
         <v>36</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>25</v>
+        <v>77</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M36" s="2" t="s">
         <v>27</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O36" s="2" t="s">
         <v>29</v>
@@ -2600,7 +2639,7 @@
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>31</v>
@@ -2612,10 +2651,10 @@
         <v>33</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>21</v>
@@ -2627,10 +2666,10 @@
         <v>36</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="L37" s="2" t="s">
         <v>26</v>
@@ -2639,7 +2678,7 @@
         <v>27</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O37" s="2" t="s">
         <v>29</v>
@@ -2647,7 +2686,7 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>31</v>
@@ -2659,10 +2698,10 @@
         <v>33</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>21</v>
@@ -2674,19 +2713,19 @@
         <v>36</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>25</v>
+        <v>126</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M38" s="2" t="s">
         <v>27</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O38" s="2" t="s">
         <v>29</v>
@@ -2694,7 +2733,7 @@
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>31</v>
@@ -2706,10 +2745,10 @@
         <v>33</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>21</v>
@@ -2721,19 +2760,19 @@
         <v>36</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>25</v>
+        <v>77</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M39" s="2" t="s">
         <v>27</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O39" s="2" t="s">
         <v>29</v>
@@ -2741,7 +2780,7 @@
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>31</v>
@@ -2753,10 +2792,10 @@
         <v>33</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>21</v>
@@ -2768,10 +2807,10 @@
         <v>36</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="L40" s="2" t="s">
         <v>26</v>
@@ -2780,7 +2819,7 @@
         <v>27</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O40" s="2" t="s">
         <v>29</v>
@@ -2788,7 +2827,7 @@
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>31</v>
@@ -2800,13 +2839,13 @@
         <v>33</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>35</v>
@@ -2815,7 +2854,7 @@
         <v>36</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="K41" s="2" t="s">
         <v>25</v>
@@ -2827,7 +2866,7 @@
         <v>27</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="O41" s="2" t="s">
         <v>29</v>
@@ -2846,23 +2885,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="B2" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="D2" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="E2" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -2870,16 +2909,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -2890,7 +2929,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <v>0</v>
+        <v>16.4</v>
       </c>
       <c r="J5" s="4">
         <v>2</v>
@@ -2898,12 +2937,12 @@
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J22" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K22">
         <v>35</v>
@@ -2919,7 +2958,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -2950,12 +2989,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="B2">
         <v>40</v>
@@ -2969,7 +3008,7 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>0</v>
+        <v>16.4</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
@@ -2979,25 +3018,25 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -3014,28 +3053,28 @@
         <v>33</v>
       </c>
       <c r="G10" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="K10">
         <v>0</v>
       </c>
       <c r="M10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="N10">
         <v>35</v>
       </c>
       <c r="P10" t="s">
-        <v>28</v>
+        <v>154</v>
       </c>
       <c r="Q10">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
@@ -3052,7 +3091,7 @@
         <v>6</v>
       </c>
       <c r="G11" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="H11">
         <v>1</v>
@@ -3064,21 +3103,21 @@
         <v>40</v>
       </c>
       <c r="M11" t="s">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="N11">
         <v>0</v>
       </c>
       <c r="P11" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="Q11">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D12" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -3090,47 +3129,41 @@
         <v>39</v>
       </c>
       <c r="J12" t="s">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="K12">
         <v>0</v>
       </c>
       <c r="M12" t="s">
-        <v>144</v>
+        <v>157</v>
       </c>
       <c r="N12">
         <v>0</v>
       </c>
       <c r="P12" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="Q12">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="7:17" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G13" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="M13" t="s">
-        <v>146</v>
+        <v>159</v>
       </c>
       <c r="N13">
         <v>0</v>
       </c>
-      <c r="P13" t="s">
-        <v>39</v>
-      </c>
-      <c r="Q13">
-        <v>7</v>
-      </c>
     </row>
     <row r="14" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G14" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -3144,7 +3177,7 @@
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M15" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -3152,7 +3185,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -3160,7 +3193,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -3168,10 +3201,10 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="20" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D20" s="1" t="s">
         <v>0</v>
       </c>
@@ -3179,7 +3212,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -3187,142 +3220,142 @@
     </row>
     <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="F21" s="2">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>31</v>
       </c>
       <c r="F22" s="2">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>31</v>
       </c>
       <c r="F23" s="2">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>31</v>
       </c>
       <c r="F24" s="2">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>31</v>
       </c>
       <c r="F25" s="2">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>51</v>
+        <v>124</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>31</v>
       </c>
       <c r="F26" s="2">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>52</v>
+        <v>125</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>51</v>
+        <v>15</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="F27" s="2">
-        <v>0</v>
+        <v>113</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>54</v>
+        <v>19</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>31</v>
       </c>
       <c r="F28" s="2">
-        <v>0</v>
+        <v>113</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>31</v>
       </c>
       <c r="F29" s="2">
-        <v>0</v>
+        <v>113</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>58</v>
+        <v>90</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>31</v>
       </c>
       <c r="F30" s="2">
-        <v>0</v>
+        <v>113</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>59</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
